--- a/web/files/九龙-启德-启德海湾 1.xlsx
+++ b/web/files/九龙-启德-启德海湾 1.xlsx
@@ -47258,34 +47258,34 @@
       </c>
       <c r="F747" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G747" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H747" s="5" t="n">
-        <v>8970000</v>
+        <v>6728000</v>
       </c>
       <c r="I747" s="5" t="n">
-        <v>29410</v>
+        <v>22059</v>
       </c>
       <c r="J747" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K747" s="5" t="n">
-        <v>6727500</v>
+        <v>6728000</v>
       </c>
       <c r="L747" s="5" t="n">
-        <v>22057</v>
+        <v>22059</v>
       </c>
       <c r="M747" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N747" s="3" t="inlineStr">
@@ -70294,7 +70294,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -70304,7 +70304,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -71184,12 +71184,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K12" s="20" t="inlineStr">
+      <c r="K12" s="21" t="inlineStr">
         <is>
           <t>K | 305呎 (1房)
-$897万
-$29,410/呎
-(在售)</t>
+$673万
+$22,059/呎
+(26年-08月-01日)</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr">

--- a/web/files/九龙-启德-启德海湾 1.xlsx
+++ b/web/files/九龙-启德-启德海湾 1.xlsx
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>6348000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>20813</v>
+        <v>20745</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>6348000</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>20813</v>
+        <v>20745</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>7218000</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>23666</v>
+        <v>23588</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>7218000</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>23666</v>
+        <v>23588</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -46506,34 +46506,34 @@
       </c>
       <c r="F735" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G735" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H735" s="5" t="n">
-        <v>9077000</v>
+        <v>6808000</v>
       </c>
       <c r="I735" s="5" t="n">
-        <v>29761</v>
+        <v>22321</v>
       </c>
       <c r="J735" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K735" s="5" t="n">
-        <v>6807750</v>
+        <v>6808000</v>
       </c>
       <c r="L735" s="5" t="n">
-        <v>22320</v>
+        <v>22321</v>
       </c>
       <c r="M735" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N735" s="3" t="inlineStr">
@@ -64772,9 +64772,9 @@
       </c>
       <c r="I8" s="21" t="inlineStr">
         <is>
-          <t>H | 305呎 (1房)
+          <t>H | 306呎 (1房)
 $635万
-$20,813/呎
+$20,745/呎
 (26年-04月-02日)</t>
         </is>
       </c>
@@ -64891,9 +64891,9 @@
       </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t>J | 305呎 (1房)
+          <t>J | 306呎 (1房)
 $722万
-$23,666/呎
+$23,588/呎
 (26年-07月-24日)</t>
         </is>
       </c>
@@ -70294,7 +70294,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -70304,7 +70304,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -71081,12 +71081,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K11" s="20" t="inlineStr">
+      <c r="K11" s="21" t="inlineStr">
         <is>
           <t>K | 305呎 (1房)
-$908万
-$29,761/呎
-(在售)</t>
+$681万
+$22,321/呎
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">

--- a/web/files/九龙-启德-启德海湾 1.xlsx
+++ b/web/files/九龙-启德-启德海湾 1.xlsx
@@ -4335,7 +4335,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -29098,7 +29098,7 @@
         </is>
       </c>
       <c r="E457" s="4" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F457" s="3" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>7572000</v>
       </c>
       <c r="I457" s="5" t="n">
-        <v>17568</v>
+        <v>17528</v>
       </c>
       <c r="J457" s="3" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>7572000</v>
       </c>
       <c r="L457" s="5" t="n">
-        <v>17568</v>
+        <v>17528</v>
       </c>
       <c r="M457" s="3" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         </is>
       </c>
       <c r="E592" s="4" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F592" s="3" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>7099000</v>
       </c>
       <c r="I592" s="5" t="n">
-        <v>16471</v>
+        <v>16433</v>
       </c>
       <c r="J592" s="3" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>7099000</v>
       </c>
       <c r="L592" s="5" t="n">
-        <v>16471</v>
+        <v>16433</v>
       </c>
       <c r="M592" s="3" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
       </c>
       <c r="G814" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H814" s="5" t="n">
@@ -64894,7 +64894,7 @@
           <t>J | 306呎 (1房)
 $722万
 $23,588/呎
-(26年-07月-24日)</t>
+(26年-08月-11日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -68475,9 +68475,9 @@
       </c>
       <c r="I12" s="21" t="inlineStr">
         <is>
-          <t>H | 431呎 (2房)
+          <t>H | 432呎 (2房)
 $757万
-$17,568/呎
+$17,528/呎
 (25年-03月-26日)</t>
         </is>
       </c>
@@ -69660,9 +69660,9 @@
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
-          <t>H | 431呎 (2房)
+          <t>H | 432呎 (2房)
 $710万
-$16,471/呎
+$16,433/呎
 (25年-02月-07日)</t>
         </is>
       </c>
@@ -71648,7 +71648,7 @@
           <t>C | 551呎 (2房)
 $1308万
 $23,739/呎
-(26年-07月-14日)</t>
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">

--- a/web/files/九龙-启德-启德海湾 1.xlsx
+++ b/web/files/九龙-启德-启德海湾 1.xlsx
@@ -3516,34 +3516,34 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>9717000</v>
+        <v>7288000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>31859</v>
+        <v>23895</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>7287750</v>
+        <v>7288000</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>23894</v>
+        <v>23895</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃(照售價減7%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -32950,7 +32950,7 @@
         </is>
       </c>
       <c r="E519" s="4" t="n">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F519" s="3" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>10255000</v>
       </c>
       <c r="I519" s="5" t="n">
-        <v>19061</v>
+        <v>19097</v>
       </c>
       <c r="J519" s="3" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>10255000</v>
       </c>
       <c r="L519" s="5" t="n">
-        <v>19061</v>
+        <v>19097</v>
       </c>
       <c r="M519" s="3" t="inlineStr">
         <is>
@@ -44164,7 +44164,7 @@
       </c>
       <c r="F698" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G698" s="3" t="inlineStr">
@@ -44172,31 +44172,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H698" s="5" t="n">
-        <v>12570000</v>
-      </c>
-      <c r="I698" s="5" t="n">
-        <v>29233</v>
+      <c r="H698" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I698" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J698" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K698" s="5" t="n">
-        <v>9427500</v>
-      </c>
-      <c r="L698" s="5" t="n">
-        <v>21924</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K698" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L698" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M698" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N698" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -44474,7 +44482,7 @@
       </c>
       <c r="F703" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G703" s="3" t="inlineStr">
@@ -44482,31 +44490,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H703" s="5" t="n">
-        <v>11730000</v>
-      </c>
-      <c r="I703" s="5" t="n">
-        <v>26720</v>
+      <c r="H703" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I703" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J703" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K703" s="5" t="n">
-        <v>8797500</v>
-      </c>
-      <c r="L703" s="5" t="n">
-        <v>20040</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K703" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L703" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M703" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N703" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -45676,7 +45692,7 @@
       </c>
       <c r="F722" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G722" s="3" t="inlineStr">
@@ -45684,31 +45700,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H722" s="5" t="n">
-        <v>12317000</v>
-      </c>
-      <c r="I722" s="5" t="n">
-        <v>28644</v>
+      <c r="H722" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I722" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J722" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K722" s="5" t="n">
-        <v>9237750</v>
-      </c>
-      <c r="L722" s="5" t="n">
-        <v>21483</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K722" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L722" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M722" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N722" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -45986,7 +46010,7 @@
       </c>
       <c r="F727" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G727" s="3" t="inlineStr">
@@ -45994,31 +46018,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H727" s="5" t="n">
-        <v>11256000</v>
-      </c>
-      <c r="I727" s="5" t="n">
-        <v>25640</v>
+      <c r="H727" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I727" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J727" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K727" s="5" t="n">
-        <v>8442000</v>
-      </c>
-      <c r="L727" s="5" t="n">
-        <v>19230</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K727" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L727" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M727" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N727" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -47196,7 +47228,7 @@
       </c>
       <c r="F746" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G746" s="3" t="inlineStr">
@@ -47204,31 +47236,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H746" s="5" t="n">
-        <v>12050000</v>
-      </c>
-      <c r="I746" s="5" t="n">
-        <v>28023</v>
+      <c r="H746" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I746" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J746" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K746" s="5" t="n">
-        <v>9037500</v>
-      </c>
-      <c r="L746" s="5" t="n">
-        <v>21017</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K746" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L746" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M746" s="3" t="inlineStr">
         <is>
-          <t>置佳時機120天即供付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N746" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -47254,7 +47294,7 @@
         </is>
       </c>
       <c r="E747" s="4" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F747" s="3" t="inlineStr">
         <is>
@@ -47263,14 +47303,14 @@
       </c>
       <c r="G747" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H747" s="5" t="n">
         <v>6728000</v>
       </c>
       <c r="I747" s="5" t="n">
-        <v>22059</v>
+        <v>21987</v>
       </c>
       <c r="J747" s="3" t="inlineStr">
         <is>
@@ -47281,7 +47321,7 @@
         <v>6728000</v>
       </c>
       <c r="L747" s="5" t="n">
-        <v>22059</v>
+        <v>21987</v>
       </c>
       <c r="M747" s="3" t="inlineStr">
         <is>
@@ -64279,7 +64319,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -64289,7 +64329,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>337</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -64778,12 +64818,12 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>J | 305呎 (1房)
-$972万
-$31,859/呎
-(在售)</t>
+$729万
+$23,895/呎
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -69036,9 +69076,9 @@
       </c>
       <c r="J19" s="21" t="inlineStr">
         <is>
-          <t>J | 538呎 (2房)
+          <t>J | 537呎 (2房)
 $1026万
-$19,061/呎
+$19,097/呎
 (25年-03月-07日)</t>
         </is>
       </c>
@@ -70294,12 +70334,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -70740,12 +70780,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 439呎 (2房)
-$1173万
-$26,720/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -70780,12 +70820,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L8" s="22" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
-$1257万
-$29,233/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -70946,12 +70986,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 439呎 (2房)
-$1126万
-$25,640/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -70986,12 +71026,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L10" s="22" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
-$1232万
-$28,644/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -71186,18 +71226,18 @@
       </c>
       <c r="K12" s="21" t="inlineStr">
         <is>
-          <t>K | 305呎 (1房)
+          <t>K | 306呎 (1房)
 $673万
-$22,059/呎
-(26年-08月-01日)</t>
-        </is>
-      </c>
-      <c r="L12" s="22" t="inlineStr">
+$21,987/呎
+(26年-08月-20日)</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
-$1205万
-$28,023/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
